--- a/output/universities/daad-programs.xlsx
+++ b/output/universities/daad-programs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="1060">
   <si>
     <t>ID</t>
   </si>
@@ -3230,6 +3230,65 @@
   </si>
   <si>
     <t>https://www.daad.de/en/studying-in-germany/universities/all-degree-programmes/detail/saarland-university-quanteninformationstheorie-w77369/?hec-id=w77369</t>
+  </si>
+  <si>
+    <t>w77616</t>
+  </si>
+  <si>
+    <t>University of Cologne</t>
+  </si>
+  <si>
+    <t>Business Analytics &amp; AI</t>
+  </si>
+  <si>
+    <t>24,900.00 EUR / total</t>
+  </si>
+  <si>
+    <t>Zusätzlich zu den Studiengebühren wird jedes Semester ein Semesterbeitrag an die Universität zu Köln fällig. Dieser beinhaltet das Deutschlandticket sowie den Zugang zu verschiedenen Studierendenservices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 days left (Germans and inhabitants)
+23 days left (EU)
+23 days left (Non-EU)</t>
+  </si>
+  <si>
+    <t>Abgeschlossenes Bachelorstudium oder ein gleichwertiger akademischer Abschluss in einem relevanten Fachbereich (s. Zielgruppe) Berufserfahrung von mind. einem Jahr Englischkenntnisse auf Niveau B2 (GER/CEFR) oder höher, da das gesamte Programm auf Englisch unterrichtet wird</t>
+  </si>
+  <si>
+    <t>https://www.daad.de/en/studying-in-germany/universities/all-degree-programmes/detail/university-of-cologne-business-analytics-ai-w77616/?hec-id=w77616</t>
+  </si>
+  <si>
+    <t>https://business-school.uni-koeln.de/de/master-baai</t>
+  </si>
+  <si>
+    <t>w77784</t>
+  </si>
+  <si>
+    <t>Future Analytics: AI &amp; Audio Worlds</t>
+  </si>
+  <si>
+    <t>- Bachelor-Abschluss - Ausreichende Englischkenntnisse (mindestens B2 Niveau) Alternativ: vollständig in Englisch absolviertes Studium - Einschlägige Studienleistungen in mindestens einem oder mehreren Bereichen aus: Sound Studies; Sound Design; Musik; : instrumentale/künstlerische Ausbildung, Musik-Wissenschaft/-Geschichte/-Vermittlung/-Pädagogik; Gender/Queer/Postcolonial/Critical Disability/Science and Technology Studies; Kulturwissenschaften, Anthropologie, Transdisziplinäre Studien; (Musik...</t>
+  </si>
+  <si>
+    <t>https://www.daad.de/en/studying-in-germany/universities/all-degree-programmes/detail/university-of-hildesheim-future-analytics-ai-audio-worlds-w77784/?hec-id=w77784</t>
+  </si>
+  <si>
+    <t>https://www.uni-hildesheim.de/studium/studieninteressierte/studiengaenge/masterstudium/future-analytics-ai-audio-worlds-msc-ma/</t>
+  </si>
+  <si>
+    <t>w77922</t>
+  </si>
+  <si>
+    <t>Pharmaceutical and Molecular Biotechnology</t>
+  </si>
+  <si>
+    <t>Ein Bachelorabschluss mit der Gesamtnote 2,7 oder besser.</t>
+  </si>
+  <si>
+    <t>https://www.daad.de/en/studying-in-germany/universities/all-degree-programmes/detail/university-of-ulm-pharmaceutical-and-molecular-biotechnology-w77922/?hec-id=w77922</t>
+  </si>
+  <si>
+    <t>https://www.uni-ulm.de/nawi/naturwissenschaften/studium/studiengaenge/studiengang/course/pharmaceutical-and-molecular-biotechnology-master/</t>
   </si>
   <si>
     <t>w7857</t>
@@ -3637,7 +3696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O174"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11601,93 +11660,234 @@
         <v>1032</v>
       </c>
       <c r="B170" t="s">
-        <v>266</v>
+        <v>1033</v>
       </c>
       <c r="C170" t="s">
-        <v>267</v>
+        <v>63</v>
       </c>
       <c r="D170" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="E170" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F170" t="s">
         <v>20</v>
       </c>
       <c r="G170" t="s">
-        <v>21</v>
+        <v>600</v>
       </c>
       <c r="H170" t="s">
-        <v>269</v>
+        <v>22</v>
       </c>
       <c r="I170" t="s">
-        <v>270</v>
+        <v>1035</v>
       </c>
       <c r="J170" t="s">
-        <v>23</v>
+        <v>1036</v>
       </c>
       <c r="K170" t="s">
         <v>24</v>
       </c>
       <c r="L170" t="s">
-        <v>90</v>
+        <v>1037</v>
       </c>
       <c r="M170" t="s">
-        <v>271</v>
+        <v>1038</v>
       </c>
       <c r="N170" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="O170" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="B171" t="s">
+        <v>347</v>
+      </c>
+      <c r="C171" t="s">
+        <v>348</v>
+      </c>
+      <c r="D171" t="s">
+        <v>291</v>
+      </c>
+      <c r="E171" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F171" t="s">
+        <v>153</v>
+      </c>
+      <c r="G171" t="s">
+        <v>21</v>
+      </c>
+      <c r="H171" t="s">
+        <v>269</v>
+      </c>
+      <c r="I171" t="s">
+        <v>23</v>
+      </c>
+      <c r="J171" t="s">
+        <v>23</v>
+      </c>
+      <c r="K171" t="s">
+        <v>24</v>
+      </c>
+      <c r="L171" t="s">
+        <v>90</v>
+      </c>
+      <c r="M171" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N171" t="s">
+        <v>1044</v>
+      </c>
+      <c r="O171" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B172" t="s">
+        <v>275</v>
+      </c>
+      <c r="C172" t="s">
+        <v>276</v>
+      </c>
+      <c r="D172" t="s">
+        <v>18</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F172" t="s">
+        <v>153</v>
+      </c>
+      <c r="G172" t="s">
+        <v>21</v>
+      </c>
+      <c r="H172" t="s">
+        <v>22</v>
+      </c>
+      <c r="I172" t="s">
+        <v>23</v>
+      </c>
+      <c r="J172" t="s">
+        <v>23</v>
+      </c>
+      <c r="K172" t="s">
+        <v>24</v>
+      </c>
+      <c r="L172" t="s">
+        <v>90</v>
+      </c>
+      <c r="M172" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N172" t="s">
+        <v>1049</v>
+      </c>
+      <c r="O172" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B173" t="s">
+        <v>266</v>
+      </c>
+      <c r="C173" t="s">
+        <v>267</v>
+      </c>
+      <c r="D173" t="s">
+        <v>104</v>
+      </c>
+      <c r="E173" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F173" t="s">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>21</v>
+      </c>
+      <c r="H173" t="s">
+        <v>269</v>
+      </c>
+      <c r="I173" t="s">
+        <v>270</v>
+      </c>
+      <c r="J173" t="s">
+        <v>23</v>
+      </c>
+      <c r="K173" t="s">
+        <v>24</v>
+      </c>
+      <c r="L173" t="s">
+        <v>90</v>
+      </c>
+      <c r="M173" t="s">
+        <v>271</v>
+      </c>
+      <c r="N173" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O173" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B174" t="s">
         <v>46</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C174" t="s">
         <v>47</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D174" t="s">
         <v>48</v>
       </c>
-      <c r="E171" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F171" t="s">
-        <v>20</v>
-      </c>
-      <c r="G171" t="s">
-        <v>21</v>
-      </c>
-      <c r="H171" t="s">
+      <c r="E174" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F174" t="s">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>21</v>
+      </c>
+      <c r="H174" t="s">
         <v>22</v>
       </c>
-      <c r="I171" t="s">
-        <v>23</v>
-      </c>
-      <c r="J171" t="s">
-        <v>23</v>
-      </c>
-      <c r="K171" t="s">
-        <v>24</v>
-      </c>
-      <c r="L171" t="s">
+      <c r="I174" t="s">
+        <v>23</v>
+      </c>
+      <c r="J174" t="s">
+        <v>23</v>
+      </c>
+      <c r="K174" t="s">
+        <v>24</v>
+      </c>
+      <c r="L174" t="s">
         <v>328</v>
       </c>
-      <c r="M171" t="s">
-        <v>1038</v>
-      </c>
-      <c r="N171" t="s">
-        <v>1039</v>
-      </c>
-      <c r="O171" t="s">
-        <v>1040</v>
+      <c r="M174" t="s">
+        <v>1057</v>
+      </c>
+      <c r="N174" t="s">
+        <v>1058</v>
+      </c>
+      <c r="O174" t="s">
+        <v>1059</v>
       </c>
     </row>
   </sheetData>
